--- a/ProductDesign/PersonaSociety.xlsx
+++ b/ProductDesign/PersonaSociety.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="PersonaSociety" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PersonaSociety!$A$1:$AD$101</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4015,32 +4018,32 @@
   <dimension ref="A1:AD101"/>
   <sheetFormatPr defaultColWidth="41.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.53125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.1328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="36.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36.06640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.53125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.9296875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.265625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="40.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="40.73046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.19921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.59765625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="41.265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.9296875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="39.06640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="40.53125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="34.73046875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="44.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
@@ -13336,6 +13339,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AD101"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ProductDesign/PersonaSociety.xlsx
+++ b/ProductDesign/PersonaSociety.xlsx
@@ -4015,7 +4015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD101"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr defaultColWidth="41.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.19921875" bestFit="1" customWidth="1"/>
@@ -4046,7 +4046,7 @@
     <col min="30" max="30" width="44.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="57" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" ht="57" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -4229,8 +4229,9 @@
       <c r="AD2" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="AE2" s="2"/>
     </row>
-    <row r="3" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -4321,8 +4322,9 @@
       <c r="AD3" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="AE3" s="2"/>
     </row>
-    <row r="4" spans="1:30" ht="57" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" ht="57" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -4413,8 +4415,9 @@
       <c r="AD4" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="AE4" s="2"/>
     </row>
-    <row r="5" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -4505,8 +4508,9 @@
       <c r="AD5" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="AE5" s="2"/>
     </row>
-    <row r="6" spans="1:30" ht="57" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" ht="57" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -4597,8 +4601,9 @@
       <c r="AD6" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="AE6" s="2"/>
     </row>
-    <row r="7" spans="1:30" ht="57" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -4689,8 +4694,9 @@
       <c r="AD7" s="1" t="s">
         <v>133</v>
       </c>
+      <c r="AE7" s="2"/>
     </row>
-    <row r="8" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -4781,8 +4787,9 @@
       <c r="AD8" s="1" t="s">
         <v>146</v>
       </c>
+      <c r="AE8" s="2"/>
     </row>
-    <row r="9" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -4873,8 +4880,9 @@
       <c r="AD9" s="1" t="s">
         <v>158</v>
       </c>
+      <c r="AE9" s="2"/>
     </row>
-    <row r="10" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -4965,8 +4973,9 @@
       <c r="AD10" s="1" t="s">
         <v>171</v>
       </c>
+      <c r="AE10" s="2"/>
     </row>
-    <row r="11" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -5057,8 +5066,9 @@
       <c r="AD11" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="AE11" s="2"/>
     </row>
-    <row r="12" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -5149,8 +5159,9 @@
       <c r="AD12" s="1" t="s">
         <v>195</v>
       </c>
+      <c r="AE12" s="2"/>
     </row>
-    <row r="13" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -5241,8 +5252,9 @@
       <c r="AD13" s="1" t="s">
         <v>209</v>
       </c>
+      <c r="AE13" s="2"/>
     </row>
-    <row r="14" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -5333,8 +5345,9 @@
       <c r="AD14" s="1" t="s">
         <v>223</v>
       </c>
+      <c r="AE14" s="2"/>
     </row>
-    <row r="15" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -5425,8 +5438,9 @@
       <c r="AD15" s="1" t="s">
         <v>236</v>
       </c>
+      <c r="AE15" s="2"/>
     </row>
-    <row r="16" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -5517,8 +5531,9 @@
       <c r="AD16" s="1" t="s">
         <v>249</v>
       </c>
+      <c r="AE16" s="2"/>
     </row>
-    <row r="17" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -5609,8 +5624,9 @@
       <c r="AD17" s="1" t="s">
         <v>261</v>
       </c>
+      <c r="AE17" s="2"/>
     </row>
-    <row r="18" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -5701,8 +5717,9 @@
       <c r="AD18" s="1" t="s">
         <v>272</v>
       </c>
+      <c r="AE18" s="2"/>
     </row>
-    <row r="19" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -5793,8 +5810,9 @@
       <c r="AD19" s="1" t="s">
         <v>284</v>
       </c>
+      <c r="AE19" s="2"/>
     </row>
-    <row r="20" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -5885,8 +5903,9 @@
       <c r="AD20" s="1" t="s">
         <v>295</v>
       </c>
+      <c r="AE20" s="2"/>
     </row>
-    <row r="21" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -5977,8 +5996,9 @@
       <c r="AD21" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="AE21" s="2"/>
     </row>
-    <row r="22" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>101</v>
       </c>
@@ -6069,8 +6089,9 @@
       <c r="AD22" s="1" t="s">
         <v>321</v>
       </c>
+      <c r="AE22" s="2"/>
     </row>
-    <row r="23" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>102</v>
       </c>
@@ -6161,8 +6182,9 @@
       <c r="AD23" s="1" t="s">
         <v>332</v>
       </c>
+      <c r="AE23" s="2"/>
     </row>
-    <row r="24" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>103</v>
       </c>
@@ -6253,8 +6275,9 @@
       <c r="AD24" s="1" t="s">
         <v>345</v>
       </c>
+      <c r="AE24" s="2"/>
     </row>
-    <row r="25" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>104</v>
       </c>
@@ -6345,8 +6368,9 @@
       <c r="AD25" s="1" t="s">
         <v>356</v>
       </c>
+      <c r="AE25" s="2"/>
     </row>
-    <row r="26" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>105</v>
       </c>
@@ -6437,8 +6461,9 @@
       <c r="AD26" s="1" t="s">
         <v>368</v>
       </c>
+      <c r="AE26" s="2"/>
     </row>
-    <row r="27" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>106</v>
       </c>
@@ -6529,8 +6554,9 @@
       <c r="AD27" s="1" t="s">
         <v>380</v>
       </c>
+      <c r="AE27" s="2"/>
     </row>
-    <row r="28" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>107</v>
       </c>
@@ -6621,8 +6647,9 @@
       <c r="AD28" s="1" t="s">
         <v>392</v>
       </c>
+      <c r="AE28" s="2"/>
     </row>
-    <row r="29" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>108</v>
       </c>
@@ -6713,8 +6740,9 @@
       <c r="AD29" s="1" t="s">
         <v>405</v>
       </c>
+      <c r="AE29" s="2"/>
     </row>
-    <row r="30" spans="1:30" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:31" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>109</v>
       </c>
@@ -6805,8 +6833,9 @@
       <c r="AD30" s="1" t="s">
         <v>418</v>
       </c>
+      <c r="AE30" s="2"/>
     </row>
-    <row r="31" spans="1:30" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:31" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>110</v>
       </c>
@@ -6897,8 +6926,9 @@
       <c r="AD31" s="1" t="s">
         <v>430</v>
       </c>
+      <c r="AE31" s="2"/>
     </row>
-    <row r="32" spans="1:30" ht="57" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:31" ht="57" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>111</v>
       </c>
